--- a/duoki_editor/resources/data/blank/商店-魔法师-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/商店-魔法师-1-blank.xlsx
@@ -88,19 +88,19 @@
     <t>没问题！{npc1_name}。你需要什么物品！快告诉我们吧！</t>
   </si>
   <si>
-    <t>太好了。请看地图！第一个神奇物品是`{word_cn}！{word_en}`</t>
-  </si>
-  <si>
-    <t>接下来。我们要找到`{word_cn}！{word_en}`</t>
-  </si>
-  <si>
-    <t>然后。请找到神奇的`{word_cn}！{word_en}`</t>
-  </si>
-  <si>
-    <t>最后一个是——神奇的`{word_cn}！{word_en}`</t>
-  </si>
-  <si>
-    <t>我来帮你找到！`{word_cn}！{word_en}`</t>
+    <t>太好了。请看地图！第一个神奇物品是{word_cn}！{word_en}</t>
+  </si>
+  <si>
+    <t>接下来。我们要找到{word_cn}！{word_en}</t>
+  </si>
+  <si>
+    <t>然后。请找到神奇的{word_cn}！{word_en}</t>
+  </si>
+  <si>
+    <t>最后一个是——神奇的{word_cn}！{word_en}</t>
+  </si>
+  <si>
+    <t>我来帮你找吧！{word_cn}！{word_en}</t>
   </si>
   <si>
     <t>teddy bear|blocks|robot|pencil|crayon|eraser|cup|puzzle|flashlight|jelly|cake|chips|lollipop|cotton candy|popcorn|water|coffee|milkshake|tea</t>
